--- a/reports/pdf_rolling5_20260729.xlsx
+++ b/reports/pdf_rolling5_20260729.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,141억   ·   현금 248억(6.5%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 8종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,706억   ·   현금 248억(6.5%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 8종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>211</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>868644800</v>
+        <v>867769150</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-171</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-11738534400</v>
+        <v>-11726701200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>950336000</v>
+        <v>949378000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-42</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-527882880</v>
+        <v>-527350740</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1385179200</v>
+        <v>1383782850</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-27</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-737899200</v>
+        <v>-737155350</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>282690240</v>
+        <v>282405270</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-25</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-375968000</v>
+        <v>-375589000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>767808000</v>
+        <v>767034000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-481417600</v>
+        <v>-480932300</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>325872000</v>
+        <v>325543500</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-19</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-709627200</v>
+        <v>-708911850</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1433241600</v>
+        <v>1431796800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-11</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-680908800</v>
+        <v>-680222400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1589184000</v>
+        <v>1587582000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-8</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-199590400</v>
+        <v>-199389200</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-638848000</v>
+        <v>-605005500</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.90%</t>
+          <t>8.63%→7.43%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-360592000</v>
+        <v>-360228500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1076,30 +1076,30 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-605616000</v>
+        <v>-638204000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>8.63%→7.43%</t>
+          <t>1.19%→0.90%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,519억   ·   현금 26억(0.8%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,347억   ·   현금 26억(0.8%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1123,7 +1123,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,359억   ·   현금 66억(3.1%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 5종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,088억   ·   현금 66억(3.1%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1400,7 +1400,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,030억   ·   현금 79억(3.6%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 4종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,953억   ·   현금 71억(3.6%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1496,7 +1496,7 @@
         <v>328</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>8327001600</v>
+        <v>7492044800</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>-246</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-16103307600</v>
+        <v>-14488612800</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>116</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2375622000</v>
+        <v>2137416000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>-7</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-4001067000</v>
+        <v>-3599876000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>71</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>2803293000</v>
+        <v>2522204000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>41</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>4485748500</v>
+        <v>4035958000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 14억(5.1%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 9종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 239억   ·   현금 14억(5.7%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 9종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1729,11 +1729,11 @@
         <v>62</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>15502480</v>
+        <v>14065320</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.45%→0.52%</t>
+          <t>0.46%→0.54%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1750,11 +1750,11 @@
         <v>-152</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-733552000</v>
+        <v>-628428800</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2.71%→0.00%</t>
+          <t>2.64%→0.00%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1773,11 +1773,11 @@
         <v>49</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>69564320</v>
+        <v>63419720</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>3.01%→3.36%</t>
+          <t>3.11%→3.48%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1794,11 +1794,11 @@
         <v>-139</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-38558600</v>
+        <v>-35811960</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>2.81%→2.74%</t>
+          <t>2.96%→2.89%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -1817,7 +1817,7 @@
         <v>33</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>59439600</v>
+        <v>52417200</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1838,11 +1838,11 @@
         <v>-81</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-245008800</v>
+        <v>-203455800</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>8.37%→7.68%</t>
+          <t>7.88%→7.23%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1861,11 +1861,11 @@
         <v>27</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>153694800</v>
+        <v>129070800</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>2.97%→3.64%</t>
+          <t>2.83%→3.47%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1882,11 +1882,11 @@
         <v>-77</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-93105320</v>
+        <v>-85205120</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>0.36%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1905,11 +1905,11 @@
         <v>13</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>25688000</v>
+        <v>23267400</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>0.72%→0.83%</t>
+          <t>0.74%→0.86%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1926,11 +1926,11 @@
         <v>-30</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-68856000</v>
+        <v>-62814000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>3.10%→2.93%</t>
+          <t>3.21%→3.03%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1949,11 +1949,11 @@
         <v>12</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>129595200</v>
+        <v>111355200</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.68%→3.25%</t>
+          <t>2.61%→3.16%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -1970,11 +1970,11 @@
         <v>-11</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-50661600</v>
+        <v>-43137600</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>2.54%→2.42%</t>
+          <t>2.45%→2.34%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -1993,11 +1993,11 @@
         <v>9</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>76266000</v>
+        <v>64432800</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.73%→3.10%</t>
+          <t>2.61%→2.97%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2014,11 +2014,11 @@
         <v>-8</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-35872000</v>
+        <v>-33744000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.51%</t>
+          <t>0.67%→0.55%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2037,11 +2037,11 @@
         <v>5</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>55480000</v>
+        <v>47690000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.75%→3.04%</t>
+          <t>2.68%→2.96%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2058,11 +2058,11 @@
         <v>-7</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-51923200</v>
+        <v>-48199200</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.19%→0.00%</t>
+          <t>0.20%→0.00%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2081,11 +2081,11 @@
         <v>4</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>35142400</v>
+        <v>30400000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.17%</t>
+          <t>0.99%→1.15%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2102,11 +2102,11 @@
         <v>-3</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-71136000</v>
+        <v>-67602000</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.75%→1.53%</t>
+          <t>1.89%→1.65%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2118,7 +2118,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 468억   ·   현금 9억(1.9%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 4종목  /  매도 7종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 454억   ·   현금 9억(1.9%)      오늘 2026-07-29  vs  5일전 2026-07-22      매수 4종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
@@ -2214,7 +2214,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>552585000</v>
+        <v>547561500</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>-607</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-767855000</v>
+        <v>-760874500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>157300000</v>
+        <v>155870000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>-593</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-688176500</v>
+        <v>-681920350</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>9</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>235125000</v>
+        <v>232987500</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>-518</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-454700400</v>
+        <v>-450566760</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>7</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>1192730000</v>
+        <v>1181887000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>-104</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-490776000</v>
+        <v>-486314400</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>-15</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-176550000</v>
+        <v>-174945000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>-8</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-260920000</v>
+        <v>-258548000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>-7</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-136598000</v>
+        <v>-135356200</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260729.xlsx
+++ b/reports/pdf_rolling5_20260729.xlsx
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-605005500</v>
+        <v>-638204000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>8.63%→7.43%</t>
+          <t>1.19%→0.90%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1076,23 +1076,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-638204000</v>
+        <v>-605005500</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.90%</t>
+          <t>8.63%→7.43%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260729.xlsx
+++ b/reports/pdf_rolling5_20260729.xlsx
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-638204000</v>
+        <v>-360228500</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.90%</t>
+          <t>0.44%→0.41%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-360228500</v>
+        <v>-605005500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.41%</t>
+          <t>8.63%→7.43%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1076,23 +1076,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-605005500</v>
+        <v>-638204000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>8.63%→7.43%</t>
+          <t>1.19%→0.90%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260729.xlsx
+++ b/reports/pdf_rolling5_20260729.xlsx
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-360228500</v>
+        <v>-638204000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.41%</t>
+          <t>1.19%→0.90%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1076,23 +1076,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-638204000</v>
+        <v>-360228500</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.90%</t>
+          <t>0.44%→0.41%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260729.xlsx
+++ b/reports/pdf_rolling5_20260729.xlsx
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-638204000</v>
+        <v>-360228500</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.90%</t>
+          <t>0.44%→0.41%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1076,23 +1076,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-360228500</v>
+        <v>-638204000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.41%</t>
+          <t>1.19%→0.90%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
